--- a/data/trans_orig/P35_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P35_2023-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su médico u otra persona le ha aconsejado que realice algún tipo de ejercicio físico en 2023</t>
+          <t>Población según si su médico u otra persona le ha aconsejado que realice algún tipo de ejercicio físico en 2023 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17024</t>
+          <t>17585</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>35731</t>
+          <t>34274</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6660</t>
+          <t>6238</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17481</t>
+          <t>17279</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>26914</t>
+          <t>26544</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>48349</t>
+          <t>49709</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,22%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5816</t>
+          <t>5759</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19446</t>
+          <t>19441</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4756</t>
+          <t>4722</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14661</t>
+          <t>15157</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>13152</t>
+          <t>12951</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>29481</t>
+          <t>29279</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,07%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>116846</t>
+          <t>118018</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>155713</t>
+          <t>158201</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>31,31%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>90296</t>
+          <t>92321</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>120450</t>
+          <t>118879</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>217070</t>
+          <t>216894</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>266007</t>
+          <t>265226</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>27,84%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>310348</t>
+          <t>310451</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>352356</t>
+          <t>354511</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>61,43%</t>
+          <t>61,45%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>69,74%</t>
+          <t>70,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>306794</t>
+          <t>307065</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>338398</t>
+          <t>336352</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>68,56%</t>
+          <t>68,62%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>75,63%</t>
+          <t>75,17%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>627196</t>
+          <t>628628</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>680676</t>
+          <t>682555</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>65,83%</t>
+          <t>65,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>71,45%</t>
+          <t>71,65%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>25439</t>
+          <t>25534</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>47989</t>
+          <t>46263</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>15137</t>
+          <t>14606</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>29600</t>
+          <t>29583</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>43233</t>
+          <t>43384</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>69834</t>
+          <t>71109</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,53%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9622</t>
+          <t>9841</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25089</t>
+          <t>25685</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9105</t>
+          <t>9008</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21425</t>
+          <t>22106</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22026</t>
+          <t>21876</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>41266</t>
+          <t>42355</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,08%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>104703</t>
+          <t>104752</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>142654</t>
+          <t>142749</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>31,57%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>93757</t>
+          <t>91804</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>123192</t>
+          <t>121955</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>208541</t>
+          <t>207668</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>255096</t>
+          <t>254032</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>30,46%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>255431</t>
+          <t>257391</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>298265</t>
+          <t>298760</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>56,48%</t>
+          <t>56,92%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>65,96%</t>
+          <t>66,07%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>221490</t>
+          <t>222570</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>253099</t>
+          <t>255494</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>58,02%</t>
+          <t>58,3%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>66,3%</t>
+          <t>66,93%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>491526</t>
+          <t>487527</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>542605</t>
+          <t>539673</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>58,94%</t>
+          <t>58,46%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>65,06%</t>
+          <t>64,71%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>12969</t>
+          <t>11915</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>67632</t>
+          <t>66521</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>7031</t>
+          <t>6979</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>16966</t>
+          <t>17248</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>16759</t>
+          <t>21040</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>75375</t>
+          <t>73905</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>8,85%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1694</t>
+          <t>2215</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>18022</t>
+          <t>18322</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1717</t>
+          <t>1704</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8950</t>
+          <t>9309</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>4749</t>
+          <t>5018</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>24377</t>
+          <t>24029</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,88%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>44139</t>
+          <t>44698</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>191531</t>
+          <t>193455</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>44870</t>
+          <t>44891</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>64402</t>
+          <t>64331</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>38,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>73205</t>
+          <t>82444</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>249123</t>
+          <t>248074</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>29,7%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>399102</t>
+          <t>398652</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>606667</t>
+          <t>606961</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>59,72%</t>
+          <t>59,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>90,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>86726</t>
+          <t>86764</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>107508</t>
+          <t>107861</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>51,96%</t>
+          <t>51,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>64,41%</t>
+          <t>64,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>494789</t>
+          <t>497477</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>737225</t>
+          <t>720514</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>59,24%</t>
+          <t>59,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,27%</t>
+          <t>86,27%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>69047</t>
+          <t>67638</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>109899</t>
+          <t>108822</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>25663</t>
+          <t>24563</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>70391</t>
+          <t>71199</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>93860</t>
+          <t>97232</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>164923</t>
+          <t>164880</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,7 +2522,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>17241</t>
+          <t>18141</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>35232</t>
+          <t>37473</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>7717</t>
+          <t>7901</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>27712</t>
+          <t>28131</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>28142</t>
+          <t>28458</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>58380</t>
+          <t>59050</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>231271</t>
+          <t>234045</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>289861</t>
+          <t>290543</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>95368</t>
+          <t>84016</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>240958</t>
+          <t>240325</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>292966</t>
+          <t>311564</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>505380</t>
+          <t>508420</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>25,28%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>627599</t>
+          <t>630130</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>695797</t>
+          <t>697765</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>60,65%</t>
+          <t>60,89%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>67,24%</t>
+          <t>67,43%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>648166</t>
+          <t>649642</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>843272</t>
+          <t>857563</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>66,37%</t>
+          <t>66,52%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>86,35%</t>
+          <t>87,82%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1303653</t>
+          <t>1301356</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1590025</t>
+          <t>1573600</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>64,81%</t>
+          <t>64,7%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>79,05%</t>
+          <t>78,24%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>31100</t>
+          <t>30525</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>60198</t>
+          <t>59471</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>48932</t>
+          <t>49560</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>82634</t>
+          <t>85210</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>87525</t>
+          <t>86662</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>134143</t>
+          <t>132621</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,09%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>9194</t>
+          <t>9598</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>22178</t>
+          <t>22763</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>16642</t>
+          <t>16770</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>33357</t>
+          <t>34067</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>28597</t>
+          <t>28279</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>50530</t>
+          <t>51486</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,92%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>78304</t>
+          <t>79971</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>112686</t>
+          <t>114475</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>182487</t>
+          <t>185213</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>284912</t>
+          <t>289166</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>34,47%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>279984</t>
+          <t>278128</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>379710</t>
+          <t>379196</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>28,86%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>300277</t>
+          <t>301306</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>344041</t>
+          <t>341178</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>63,21%</t>
+          <t>63,43%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>72,42%</t>
+          <t>71,82%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>454150</t>
+          <t>448498</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>599305</t>
+          <t>581577</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>54,13%</t>
+          <t>53,46%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>71,43%</t>
+          <t>69,32%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>776075</t>
+          <t>775608</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>909245</t>
+          <t>919239</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>59,06%</t>
+          <t>59,02%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>69,96%</t>
         </is>
       </c>
     </row>
@@ -3575,12 +3575,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>10683</t>
+          <t>11006</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>39139</t>
+          <t>40041</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>71989</t>
+          <t>73550</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>105024</t>
+          <t>108573</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>90488</t>
+          <t>88428</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>136214</t>
+          <t>135705</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,56%</t>
         </is>
       </c>
     </row>
@@ -3688,12 +3688,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>168</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>15201</t>
+          <t>14758</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>26163</t>
+          <t>25388</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>47172</t>
+          <t>45708</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3738,12 +3738,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>28795</t>
+          <t>29042</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>52293</t>
+          <t>52971</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3773,12 +3773,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,29%</t>
         </is>
       </c>
     </row>
@@ -3801,12 +3801,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>8823</t>
+          <t>8631</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>30521</t>
+          <t>29286</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>171835</t>
+          <t>170623</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>214719</t>
+          <t>211078</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3851,12 +3851,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>187188</t>
+          <t>185120</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>237488</t>
+          <t>233387</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3886,12 +3886,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,32%</t>
         </is>
       </c>
     </row>
@@ -3914,12 +3914,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>177943</t>
+          <t>177405</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>212719</t>
+          <t>213838</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3929,12 +3929,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>73,99%</t>
+          <t>73,76%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>88,91%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3949,12 +3949,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>419251</t>
+          <t>419089</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>470765</t>
+          <t>470404</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3964,12 +3964,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>55,13%</t>
+          <t>55,11%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>61,91%</t>
+          <t>61,86%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3984,12 +3984,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>611820</t>
+          <t>611763</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>673992</t>
+          <t>677523</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>61,13%</t>
+          <t>61,12%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>67,34%</t>
+          <t>67,69%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>197096</t>
+          <t>194023</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>290911</t>
+          <t>290816</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>201195</t>
+          <t>203868</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>287395</t>
+          <t>283724</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>426233</t>
+          <t>430724</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>556420</t>
+          <t>556035</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,0%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>62647</t>
+          <t>64179</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>102392</t>
+          <t>101569</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>82697</t>
+          <t>83061</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>125659</t>
+          <t>125982</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>155244</t>
+          <t>158642</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>213991</t>
+          <t>214275</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4370,12 +4370,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>569908</t>
+          <t>593789</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>824130</t>
+          <t>823721</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4385,12 +4385,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>716637</t>
+          <t>730654</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>974345</t>
+          <t>974657</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1418710</t>
+          <t>1426412</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1760458</t>
+          <t>1762002</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,36%</t>
         </is>
       </c>
     </row>
@@ -4483,12 +4483,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>2196852</t>
+          <t>2195013</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2559428</t>
+          <t>2534533</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>65,07%</t>
+          <t>65,02%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>75,81%</t>
+          <t>75,07%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>2214655</t>
+          <t>2218576</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>2567805</t>
+          <t>2555762</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>62,0%</t>
+          <t>62,11%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>71,88%</t>
+          <t>71,55%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>4462727</t>
+          <t>4457345</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>4929297</t>
+          <t>4928315</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>64,23%</t>
+          <t>64,15%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>70,94%</t>
+          <t>70,93%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P35_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P35_2023-Clase-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>24917</t>
+          <t>27085</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17585</t>
+          <t>18749</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>34274</t>
+          <t>38733</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>11016</t>
+          <t>12179</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6238</t>
+          <t>7419</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17279</t>
+          <t>18350</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>35932</t>
+          <t>39264</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>26544</t>
+          <t>29310</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>49709</t>
+          <t>53132</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,11%</t>
         </is>
       </c>
     </row>
@@ -838,17 +838,17 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11418</t>
+          <t>12451</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5759</t>
+          <t>6344</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19441</t>
+          <t>21186</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8736</t>
+          <t>9716</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4722</t>
+          <t>5445</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15157</t>
+          <t>17118</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>20154</t>
+          <t>22168</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>12951</t>
+          <t>14472</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>29279</t>
+          <t>33371</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>136463</t>
+          <t>156799</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>118018</t>
+          <t>136529</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>158201</t>
+          <t>181788</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>28,48%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>31,31%</t>
+          <t>33,02%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>104795</t>
+          <t>116249</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>92321</t>
+          <t>100164</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>118879</t>
+          <t>132425</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>241258</t>
+          <t>273048</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>216894</t>
+          <t>246397</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>265226</t>
+          <t>300940</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>28,96%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>332414</t>
+          <t>354283</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>310451</t>
+          <t>329212</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>354511</t>
+          <t>377163</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>65,8%</t>
+          <t>64,34%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>61,45%</t>
+          <t>59,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>70,17%</t>
+          <t>68,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>322920</t>
+          <t>350267</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>307065</t>
+          <t>332736</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>336352</t>
+          <t>367097</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>72,17%</t>
+          <t>71,72%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>68,62%</t>
+          <t>68,13%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>75,17%</t>
+          <t>75,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>655335</t>
+          <t>704550</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>628628</t>
+          <t>673131</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>682555</t>
+          <t>731572</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>68,79%</t>
+          <t>67,81%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>65,99%</t>
+          <t>64,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>71,65%</t>
+          <t>70,41%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>35218</t>
+          <t>41097</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>25534</t>
+          <t>30661</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>46263</t>
+          <t>55154</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>21395</t>
+          <t>23442</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>14606</t>
+          <t>16126</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>29583</t>
+          <t>32191</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>56613</t>
+          <t>64539</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>43384</t>
+          <t>50888</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>71109</t>
+          <t>80502</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,89%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>16129</t>
+          <t>18858</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9841</t>
+          <t>11902</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25685</t>
+          <t>30751</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>14451</t>
+          <t>15672</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9008</t>
+          <t>9906</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22106</t>
+          <t>23950</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>30581</t>
+          <t>34531</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21876</t>
+          <t>24900</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>42355</t>
+          <t>48082</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,31%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>122992</t>
+          <t>129277</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>104752</t>
+          <t>109186</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>142749</t>
+          <t>147392</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>107109</t>
+          <t>119913</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>91804</t>
+          <t>103705</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>121955</t>
+          <t>136845</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>32,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>230101</t>
+          <t>249190</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>207668</t>
+          <t>224836</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>254032</t>
+          <t>275723</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>30,45%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>277874</t>
+          <t>293980</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>257391</t>
+          <t>274228</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>298760</t>
+          <t>318720</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>61,45%</t>
+          <t>60,84%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>56,92%</t>
+          <t>56,75%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>66,07%</t>
+          <t>65,96%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>238793</t>
+          <t>263250</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>222570</t>
+          <t>246899</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>255494</t>
+          <t>279884</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>62,55%</t>
+          <t>62,34%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>58,3%</t>
+          <t>58,47%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>66,93%</t>
+          <t>66,28%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>516666</t>
+          <t>557230</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>487527</t>
+          <t>526256</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>539673</t>
+          <t>584350</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>61,95%</t>
+          <t>61,54%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>58,46%</t>
+          <t>58,12%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>64,71%</t>
+          <t>64,53%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>381749</t>
+          <t>422278</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>381749</t>
+          <t>422278</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>381749</t>
+          <t>422278</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>833961</t>
+          <t>905490</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>833961</t>
+          <t>905490</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>833961</t>
+          <t>905490</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>38487</t>
+          <t>42004</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>11915</t>
+          <t>31311</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>66521</t>
+          <t>56960</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>11003</t>
+          <t>12105</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6979</t>
+          <t>7440</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>17248</t>
+          <t>18527</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>49490</t>
+          <t>54108</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>21040</t>
+          <t>41796</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>73905</t>
+          <t>70386</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>10,68%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9461</t>
+          <t>12151</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2215</t>
+          <t>6384</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>18322</t>
+          <t>19957</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4209</t>
+          <t>4794</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1704</t>
+          <t>2045</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9309</t>
+          <t>10285</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>13670</t>
+          <t>16945</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>5018</t>
+          <t>10459</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>24029</t>
+          <t>25843</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,92%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>116379</t>
+          <t>127587</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>44698</t>
+          <t>108745</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>193455</t>
+          <t>146508</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>53965</t>
+          <t>60594</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>44891</t>
+          <t>49847</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>64331</t>
+          <t>72322</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>38,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>170344</t>
+          <t>188181</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>82444</t>
+          <t>168704</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>248074</t>
+          <t>210661</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>28,55%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>31,96%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>503937</t>
+          <t>289870</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>398652</t>
+          <t>269157</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>606961</t>
+          <t>310187</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>75,41%</t>
+          <t>61,46%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>59,65%</t>
+          <t>57,07%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>65,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>97734</t>
+          <t>110004</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>86764</t>
+          <t>97649</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>107861</t>
+          <t>121734</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>58,55%</t>
+          <t>58,67%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>51,98%</t>
+          <t>52,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>64,62%</t>
+          <t>64,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>601671</t>
+          <t>399875</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>497477</t>
+          <t>378643</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>720514</t>
+          <t>424709</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>72,04%</t>
+          <t>60,67%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>59,57%</t>
+          <t>57,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>64,44%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>85254</t>
+          <t>96635</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>67638</t>
+          <t>77887</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>108822</t>
+          <t>122172</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>51035</t>
+          <t>60296</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>24563</t>
+          <t>47264</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>71199</t>
+          <t>76403</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>136289</t>
+          <t>156931</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>97232</t>
+          <t>133654</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>164880</t>
+          <t>185354</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>9,31%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>25974</t>
+          <t>30310</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>18141</t>
+          <t>20955</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>37473</t>
+          <t>43140</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>17542</t>
+          <t>19144</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>7901</t>
+          <t>12432</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>28131</t>
+          <t>28790</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>43515</t>
+          <t>49454</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>28458</t>
+          <t>36957</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>59050</t>
+          <t>62984</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,16%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>259908</t>
+          <t>283156</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>234045</t>
+          <t>254115</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>290543</t>
+          <t>312769</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>184130</t>
+          <t>203068</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>84016</t>
+          <t>183685</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>240325</t>
+          <t>226193</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>444038</t>
+          <t>486224</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>311564</t>
+          <t>451968</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>508420</t>
+          <t>524672</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>26,35%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>663684</t>
+          <t>721742</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>630130</t>
+          <t>686075</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>697765</t>
+          <t>756038</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>64,14%</t>
+          <t>63,77%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>60,89%</t>
+          <t>60,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>67,43%</t>
+          <t>66,8%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>723849</t>
+          <t>577135</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>649642</t>
+          <t>548909</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>857563</t>
+          <t>600766</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>74,12%</t>
+          <t>67,14%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>66,52%</t>
+          <t>63,85%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>69,89%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1387533</t>
+          <t>1298876</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1301356</t>
+          <t>1254737</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1573600</t>
+          <t>1337414</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>68,98%</t>
+          <t>65,22%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>64,7%</t>
+          <t>63,01%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>78,24%</t>
+          <t>67,16%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>976556</t>
+          <t>859643</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>976556</t>
+          <t>859643</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>976556</t>
+          <t>859643</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2011375</t>
+          <t>1991486</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2011375</t>
+          <t>1991486</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2011375</t>
+          <t>1991486</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>42829</t>
+          <t>50896</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>30525</t>
+          <t>38159</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>59471</t>
+          <t>69749</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>67240</t>
+          <t>77617</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>49560</t>
+          <t>65053</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>85210</t>
+          <t>94699</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>110069</t>
+          <t>128513</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>86662</t>
+          <t>109526</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>132621</t>
+          <t>149507</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,69%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>14749</t>
+          <t>17162</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>9598</t>
+          <t>10627</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>22763</t>
+          <t>24864</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>24450</t>
+          <t>30538</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>16770</t>
+          <t>22196</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>34067</t>
+          <t>40957</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>39199</t>
+          <t>47700</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>28279</t>
+          <t>36096</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>51486</t>
+          <t>60959</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,36%</t>
         </is>
       </c>
     </row>
@@ -3227,32 +3227,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>95011</t>
+          <t>103194</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>79971</t>
+          <t>85490</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>114475</t>
+          <t>121637</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>247758</t>
+          <t>270307</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>185213</t>
+          <t>248926</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>289166</t>
+          <t>292779</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>32,56%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>35,27%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>342769</t>
+          <t>373501</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>278128</t>
+          <t>345234</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>379196</t>
+          <t>402592</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>28,8%</t>
         </is>
       </c>
     </row>
@@ -3340,32 +3340,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>322457</t>
+          <t>396711</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>301306</t>
+          <t>369211</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>341178</t>
+          <t>418198</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>67,88%</t>
+          <t>69,85%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>63,43%</t>
+          <t>65,01%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>71,82%</t>
+          <t>73,63%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,32 +3375,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>499548</t>
+          <t>451666</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>448498</t>
+          <t>427063</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>581577</t>
+          <t>473764</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>59,54%</t>
+          <t>54,41%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>53,46%</t>
+          <t>51,45%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>69,32%</t>
+          <t>57,07%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>822004</t>
+          <t>848377</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>775608</t>
+          <t>811481</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>919239</t>
+          <t>880593</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>62,56%</t>
+          <t>60,68%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>59,02%</t>
+          <t>58,04%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>69,96%</t>
+          <t>62,99%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1314041</t>
+          <t>1398091</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1314041</t>
+          <t>1398091</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1314041</t>
+          <t>1398091</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3555,7 +3555,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -3570,32 +3570,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>21963</t>
+          <t>25074</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>11006</t>
+          <t>12861</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>40041</t>
+          <t>43470</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,32 +3605,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>88590</t>
+          <t>106684</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>73550</t>
+          <t>87556</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>108573</t>
+          <t>129079</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,32 +3640,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>110553</t>
+          <t>131758</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>88428</t>
+          <t>107673</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>135705</t>
+          <t>157655</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>14,59%</t>
         </is>
       </c>
     </row>
@@ -3683,32 +3683,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>4098</t>
+          <t>6174</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>1736</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>14758</t>
+          <t>17973</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3718,32 +3718,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>34546</t>
+          <t>38671</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>25388</t>
+          <t>29625</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>45708</t>
+          <t>52048</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,32 +3753,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>38644</t>
+          <t>44845</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>29042</t>
+          <t>32780</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>52971</t>
+          <t>60085</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,56%</t>
         </is>
       </c>
     </row>
@@ -3796,32 +3796,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>16473</t>
+          <t>19429</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>8631</t>
+          <t>9795</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>29286</t>
+          <t>33921</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3831,32 +3831,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>192435</t>
+          <t>208537</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>170623</t>
+          <t>188785</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>211078</t>
+          <t>232667</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3866,32 +3866,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>208909</t>
+          <t>227966</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>185120</t>
+          <t>202783</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>233387</t>
+          <t>253324</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,45%</t>
         </is>
       </c>
     </row>
@@ -3909,32 +3909,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>197973</t>
+          <t>186551</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>177405</t>
+          <t>163829</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>213838</t>
+          <t>202479</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>82,32%</t>
+          <t>78,64%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>73,76%</t>
+          <t>69,06%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>85,35%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3944,32 +3944,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>444853</t>
+          <t>489367</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>419089</t>
+          <t>459482</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>470404</t>
+          <t>514859</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>58,5%</t>
+          <t>58,03%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>55,11%</t>
+          <t>54,49%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>61,86%</t>
+          <t>61,06%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3979,32 +3979,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>642826</t>
+          <t>675918</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>611763</t>
+          <t>642558</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>677523</t>
+          <t>708613</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>64,22%</t>
+          <t>62,56%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>61,12%</t>
+          <t>59,47%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>67,69%</t>
+          <t>65,58%</t>
         </is>
       </c>
     </row>
@@ -4022,17 +4022,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4057,17 +4057,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>760424</t>
+          <t>843259</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>760424</t>
+          <t>843259</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>760424</t>
+          <t>843259</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4092,17 +4092,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>1000931</t>
+          <t>1080487</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1000931</t>
+          <t>1080487</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1000931</t>
+          <t>1080487</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4139,32 +4139,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>248667</t>
+          <t>282790</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>194023</t>
+          <t>251221</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>290816</t>
+          <t>325646</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4174,32 +4174,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>250279</t>
+          <t>292323</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>203868</t>
+          <t>262645</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>283724</t>
+          <t>322770</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4209,32 +4209,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>498946</t>
+          <t>575113</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>430724</t>
+          <t>531132</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>556035</t>
+          <t>626865</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,86%</t>
         </is>
       </c>
     </row>
@@ -4252,32 +4252,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>81829</t>
+          <t>97107</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>64179</t>
+          <t>78941</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>101569</t>
+          <t>118844</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4287,32 +4287,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>103934</t>
+          <t>118536</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>83061</t>
+          <t>100699</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>125982</t>
+          <t>137165</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4322,32 +4322,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>185763</t>
+          <t>215643</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>158642</t>
+          <t>190873</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>214275</t>
+          <t>244444</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -4365,32 +4365,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>747227</t>
+          <t>819442</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>593789</t>
+          <t>770584</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>823721</t>
+          <t>873074</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4400,32 +4400,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>890192</t>
+          <t>978667</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>730654</t>
+          <t>934126</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>974657</t>
+          <t>1029513</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4435,32 +4435,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>1637419</t>
+          <t>1798110</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1426412</t>
+          <t>1726988</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1762002</t>
+          <t>1868564</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>26,42%</t>
         </is>
       </c>
     </row>
@@ -4478,32 +4478,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>2298337</t>
+          <t>2243136</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>2195013</t>
+          <t>2184044</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2534533</t>
+          <t>2302476</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>68,08%</t>
+          <t>65,16%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>65,02%</t>
+          <t>63,44%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>75,07%</t>
+          <t>66,88%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4513,32 +4513,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>2327697</t>
+          <t>2241690</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>2218576</t>
+          <t>2187663</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>2555762</t>
+          <t>2290900</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>65,16%</t>
+          <t>61,73%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>62,11%</t>
+          <t>60,25%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>71,55%</t>
+          <t>63,09%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4548,32 +4548,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>4626035</t>
+          <t>4484826</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>4457345</t>
+          <t>4404000</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>4928315</t>
+          <t>4564330</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>66,58%</t>
+          <t>63,4%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>64,15%</t>
+          <t>62,26%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>70,93%</t>
+          <t>64,53%</t>
         </is>
       </c>
     </row>
@@ -4591,17 +4591,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4626,17 +4626,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>3572102</t>
+          <t>3631216</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>3572102</t>
+          <t>3631216</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>3572102</t>
+          <t>3631216</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4661,17 +4661,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>6948163</t>
+          <t>7073692</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>6948163</t>
+          <t>7073692</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>6948163</t>
+          <t>7073692</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
